--- a/artfynd/A 364-2026 artfynd.xlsx
+++ b/artfynd/A 364-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ142"/>
+  <dimension ref="A1:AZ163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4450,10 +4450,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>68113380</v>
+        <v>137418720</v>
       </c>
       <c r="B30" t="n">
-        <v>43428</v>
+        <v>43487</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4488,24 +4488,13 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hummelsvedjevägen, Upl</t>
+          <t>Fjärilsvägen norra, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -4515,7 +4504,7 @@
         <v>6661697</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4539,12 +4528,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4553,6 +4542,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4566,20 +4556,25 @@
           <t>Fraxinus excelsior</t>
         </is>
       </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fraxinus excelsior # 3 m upp</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Arvid Löf</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Arvid Löf, Jan-Olov Björklund</t>
+          <t>Tore Dahlberg, Veronica Lindström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4589,7 +4584,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68113380</t>
+          <t>https://artportalen.se/Sighting/137418720</t>
         </is>
       </c>
     </row>
@@ -7775,10 +7770,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>80758638</v>
+        <v>137418678</v>
       </c>
       <c r="B53" t="n">
-        <v>43428</v>
+        <v>43487</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7805,7 +7800,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7813,16 +7808,10 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fjärilsvägen norra, Upl</t>
@@ -7835,7 +7824,7 @@
         <v>6661694</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7859,12 +7848,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7873,6 +7862,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7886,20 +7876,25 @@
           <t>Viburnum opulus</t>
         </is>
       </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Viburnum opulus</t>
+          <t>Viburnum opulus # 1 m upp</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Arvid Löf</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Arvid Löf, Jan-Olov Björklund</t>
+          <t>Tore Dahlberg, Veronica Lindström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -7909,7 +7904,7 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80758638</t>
+          <t>https://artportalen.se/Sighting/137418678</t>
         </is>
       </c>
     </row>
@@ -18617,10 +18612,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121062641</v>
+        <v>137418691</v>
       </c>
       <c r="B133" t="n">
-        <v>43428</v>
+        <v>43487</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -18647,7 +18642,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -18655,11 +18650,7 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
@@ -18675,7 +18666,7 @@
         <v>6661673</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -18699,17 +18690,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>2 m upp.</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -18732,30 +18718,35 @@
           <t>Fraxinus excelsior</t>
         </is>
       </c>
+      <c r="AL133" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fraxinus excelsior # 2 m upp</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Ward Tamsyn, Tore Dahlberg</t>
+          <t>Tore Dahlberg, Veronica Lindström</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asknätfjäril i AB län </t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121062641</t>
+          <t>https://artportalen.se/Sighting/137418691</t>
         </is>
       </c>
     </row>
@@ -19913,53 +19904,61 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>78165259</v>
+        <v>137418671</v>
       </c>
       <c r="B142" t="n">
-        <v>102241</v>
+        <v>43487</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221235</v>
+        <v>100943</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Hummelsvedjan, Fjärilsstigen, ca 100 m SO om vägen, Upl</t>
+          <t>Fjärilsvägen norra, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>691709</v>
+        <v>691747</v>
       </c>
       <c r="R142" t="n">
-        <v>6661552</v>
+        <v>6661707</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -19983,12 +19982,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -19997,27 +19996,2959 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>Gammalt hygge. Örtrikt</t>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 1 m upp</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418671</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>137418673</v>
+      </c>
+      <c r="B143" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>691749</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6661706</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL143" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418673</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>137418679</v>
+      </c>
+      <c r="B144" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>691744</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6661689</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418679</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>137418681</v>
+      </c>
+      <c r="B145" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>691742</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6661689</v>
+      </c>
+      <c r="S145" t="n">
+        <v>5</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418681</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>137418682</v>
+      </c>
+      <c r="B146" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>691743</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6661687</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418682</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>137418683</v>
+      </c>
+      <c r="B147" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>691747</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6661685</v>
+      </c>
+      <c r="S147" t="n">
+        <v>5</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418683</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>137418684</v>
+      </c>
+      <c r="B148" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>691767</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6661664</v>
+      </c>
+      <c r="S148" t="n">
+        <v>5</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418684</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>137418687</v>
+      </c>
+      <c r="B149" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>691767</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6661668</v>
+      </c>
+      <c r="S149" t="n">
+        <v>5</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418687</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>137418693</v>
+      </c>
+      <c r="B150" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>691769</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6661677</v>
+      </c>
+      <c r="S150" t="n">
+        <v>5</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418693</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>137418695</v>
+      </c>
+      <c r="B151" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>691767</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6661677</v>
+      </c>
+      <c r="S151" t="n">
+        <v>5</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>4 m upp</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 4 m upp</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418695</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>137418698</v>
+      </c>
+      <c r="B152" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>691771</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6661679</v>
+      </c>
+      <c r="S152" t="n">
+        <v>5</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418698</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>137418700</v>
+      </c>
+      <c r="B153" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>691768</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6661682</v>
+      </c>
+      <c r="S153" t="n">
+        <v>5</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418700</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>137418702</v>
+      </c>
+      <c r="B154" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>691768</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6661683</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418702</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>137418703</v>
+      </c>
+      <c r="B155" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>691772</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6661687</v>
+      </c>
+      <c r="S155" t="n">
+        <v>5</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418703</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>137418709</v>
+      </c>
+      <c r="B156" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>691769</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6661686</v>
+      </c>
+      <c r="S156" t="n">
+        <v>5</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418709</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>137418713</v>
+      </c>
+      <c r="B157" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>691764</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6661695</v>
+      </c>
+      <c r="S157" t="n">
+        <v>5</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418713</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>137418716</v>
+      </c>
+      <c r="B158" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>691770</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6661694</v>
+      </c>
+      <c r="S158" t="n">
+        <v>5</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL158" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418716</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>137418718</v>
+      </c>
+      <c r="B159" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>691772</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6661700</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418718</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>137418722</v>
+      </c>
+      <c r="B160" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>691767</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6661698</v>
+      </c>
+      <c r="S160" t="n">
+        <v>5</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418722</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>137418723</v>
+      </c>
+      <c r="B161" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>691763</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6661705</v>
+      </c>
+      <c r="S161" t="n">
+        <v>5</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL161" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418723</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>137418726</v>
+      </c>
+      <c r="B162" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen norra, Upl</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>691769</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6661704</v>
+      </c>
+      <c r="S162" t="n">
+        <v>5</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137418726</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>78165259</v>
+      </c>
+      <c r="B163" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Fjärilsstigen, ca 100 m SO om vägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>691709</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6661552</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2019-05-29</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2019-05-29</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>Gammalt hygge. Örtrikt</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
+      <c r="AX163" t="inlineStr">
         <is>
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY142" t="inlineStr"/>
-      <c r="AZ142" t="inlineStr">
+      <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/78165259</t>
         </is>
@@ -20166,6 +23097,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
